--- a/panel/arizalar.xlsx
+++ b/panel/arizalar.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-15 05:34:18</t>
+          <t>2026-10-15 05:35:26</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-14 22:34:18</t>
+          <t>2026-10-14 22:35:26</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -578,7 +578,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14 15:34:18</t>
+          <t>2026-10-14 15:35:26</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-14 08:34:18</t>
+          <t>2026-10-14 08:35:26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-14 01:34:18</t>
+          <t>2026-10-14 01:35:26</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -720,7 +720,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-13 18:34:18</t>
+          <t>2026-10-13 18:35:26</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">

--- a/panel/arizalar.xlsx
+++ b/panel/arizalar.xlsx
@@ -8,16 +8,22 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arizalar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hisobot" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Arizalar'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="DD.MM.YYYY HH:MM"/>
+  </numFmts>
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,17 +33,96 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="0013236A"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <color rgb="008A7D72"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="006B625A"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009A4A00"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0013236A"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="004B2C8F"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E7A3E"/>
+    </font>
+    <font>
+      <color rgb="008A7D72"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0013236A"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FF8C00"/>
+      <sz val="22"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="0013236A"/>
+      <sz val="12"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0013236A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F1EEEA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE7CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E6EBFA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEE6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E5F4EA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -45,13 +130,57 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color rgb="00FF8C00"/>
+      </left>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -126,6 +255,348 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Holatlar</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <pieChart>
+        <varyColors val="1"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Hisobot'!B8</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="FF8C00"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="13236A"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7C5CBF"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="2E9E57"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="4"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="B8AFA6"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <cat>
+            <numRef>
+              <f>'Hisobot'!$A$9:$A$13</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Hisobot'!$B$9:$B$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <dLbls>
+          <showLegendKey val="0"/>
+          <showVal val="0"/>
+          <showCatName val="0"/>
+          <showSerName val="0"/>
+          <showPercent val="1"/>
+          <showLeaderLines val="0"/>
+        </dLbls>
+        <firstSliceAng val="0"/>
+      </pieChart>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Hisobot'!B29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="13236A"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="13236A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Hisobot'!$A$30</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Hisobot'!$B$30</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Hisobot'!C29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="FF8C00"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="FF8C00"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Hisobot'!$A$30</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Hisobot'!$C$30</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="t"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6120000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5040000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Arizalar" displayName="Arizalar" ref="A4:K10" headerRowCount="1">
+  <autoFilter ref="A4:K10"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="№"/>
+    <tableColumn id="2" name="Sana"/>
+    <tableColumn id="3" name="Ism"/>
+    <tableColumn id="4" name="Telefon"/>
+    <tableColumn id="5" name="Kim"/>
+    <tableColumn id="6" name="Nima kerak"/>
+    <tableColumn id="7" name="Izohi"/>
+    <tableColumn id="8" name="Holati"/>
+    <tableColumn id="9" name="Mas’ul"/>
+    <tableColumn id="10" name="Oxirgi harakat"/>
+    <tableColumn id="11" name="Qayerdan"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Holat" displayName="Holat" ref="A8:C13" headerRowCount="1">
+  <autoFilter ref="A8:C13"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Holati"/>
+    <tableColumn id="2" name="Soni"/>
+    <tableColumn id="3" name="Ulushi"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="Oylar" displayName="Oylar" ref="A29:C30" headerRowCount="1">
+  <autoFilter ref="A29:C30"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Oy"/>
+    <tableColumn id="2" name="Arizalar"/>
+    <tableColumn id="3" name="Shartnoma"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="Ehtiyoj" displayName="Ehtiyoj" ref="A47:C53" headerRowCount="1">
+  <autoFilter ref="A47:C53"/>
+  <tableColumns count="3">
+    <tableColumn id="1" name="Nima kerak"/>
+    <tableColumn id="2" name="Soni"/>
+    <tableColumn id="3" name="Shartnoma"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="Masul" displayName="Masul" ref="A56:D59" headerRowCount="1">
+  <autoFilter ref="A56:D59"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="Xodim"/>
+    <tableColumn id="2" name="Arizalar"/>
+    <tableColumn id="3" name="Shartnoma"/>
+    <tableColumn id="4" name="Javob kutmoqda"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -415,356 +886,785 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="40" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="26" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>Arizalar daftari</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>«Oltinko‘l tuman charm-poyabzal kichik sanoat zonasini boshqarish direksiyasi» MChJ · 15.10.2026 13:00 holatiga · jami 6 ta</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Vaqt</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Sana</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Ism</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>Telefon</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>Kim</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Nima kerak</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Izoh</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Holat</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Izohi</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Holati</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Mas’ul</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Sahifa</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Oxirgi harakat</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Qayerdan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>46310.25</v>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Namuna mijoz 6</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>+998 99 666 77 88</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Donali xaridor</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Boshqa savol</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>Rad / bekor</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>Direksiya (namuna)</t>
+        </is>
+      </c>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:00 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>oltinkol-zona</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>46309.95833333334</v>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Namuna mijoz 5</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>+998 97 555 66 77</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Ishlab chiqaruvchi</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>Soliq maslahati</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="9" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr"/>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>oltinkol-zona</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>46309.66666666666</v>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Namuna mijoz 4</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>+998 94 444 55 66</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Ish izlovchi</t>
+        </is>
+      </c>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>Ishga joylashish</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>Poyabzal tikuvchi</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>oltinkol-zona</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>46309.375</v>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Namuna mijoz 3</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>+998 93 333 44 55</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Investor</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>Investitsiya</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>Bog‘lanildi</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>Direksiya (namuna)</t>
+        </is>
+      </c>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:00 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>oltinkol-zona</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>46309.08333333334</v>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Namuna mijoz 2</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>+998 91 222 33 44</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Ulgurji xaridor</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>Ulgurji xarid</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Erkaklar poyabzali, 500 juft</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>Uchrashuv belgilandi</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>Sotuv bo‘limi (namuna)</t>
+        </is>
+      </c>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:00 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>oltinkol-zona</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>46308.79166666666</v>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Namuna mijoz 1</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>+998 90 111 22 33</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Ishlab chiqaruvchi</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Savdo do‘konini kreditga olish</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>A-05 do‘kon bo‘yicha</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
+          <t>Shartnoma</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>Sotuv bo‘limi (namuna)</t>
+        </is>
+      </c>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15 13:00 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>oltinkol-zona</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A1:K1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H59"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Arizalar bo‘yicha hisobot</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>«Oltinko‘l tuman charm-poyabzal kichik sanoat zonasini boshqarish direksiyasi» MChJ · 15.10.2026 13:00 holatiga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Jami arizalar</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Yangi (javob kutmoqda)</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>Shartnoma</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>Natija (shartnoma / jami)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-10-15 05:35:26</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Namuna mijoz 6</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+998 99 666 77 88</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Donali xaridor</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="C5" s="14" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Holati bo‘yicha</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>Holati</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>Soni</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Ulushi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Yangi</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="18" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bog‘lanildi</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="18" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Uchrashuv belgilandi</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="18" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Shartnoma</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="18" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Rad / bekor</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="18" t="n">
+        <v>0.1666666666666667</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="inlineStr">
+        <is>
+          <t>Oylar bo‘yicha</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>Oy</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Arizalar</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>Shartnoma</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>oktabr 2026</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>6</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="inlineStr">
+        <is>
+          <t>Nima kerak bo‘yicha</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="17" t="inlineStr">
+        <is>
+          <t>Nima kerak</t>
+        </is>
+      </c>
+      <c r="B47" s="17" t="inlineStr">
+        <is>
+          <t>Soni</t>
+        </is>
+      </c>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>Shartnoma</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Boshqa savol</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Rad / bekor</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Soliq maslahati</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Ishga joylashish</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Investitsiya</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Ulgurji xarid</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Savdo do‘konini kreditga olish</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="inlineStr">
+        <is>
+          <t>Mas’ul xodim bo‘yicha</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>Xodim</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>Arizalar</t>
+        </is>
+      </c>
+      <c r="C56" s="17" t="inlineStr">
+        <is>
+          <t>Shartnoma</t>
+        </is>
+      </c>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>Javob kutmoqda</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>Direksiya (namuna)</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>https://linverno-tm.github.io/oltinkol-zona/</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-10-14 22:35:26</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Namuna mijoz 5</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>+998 97 555 66 77</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Ishlab chiqaruvchi</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Soliq maslahati</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Yangi</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>https://linverno-tm.github.io/oltinkol-zona/</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-10-14 15:35:26</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Namuna mijoz 4</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>+998 94 444 55 66</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Ish izlovchi</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Ishga joylashish</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Poyabzal tikuvchi</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Yangi</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>https://linverno-tm.github.io/oltinkol-zona/</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-10-14 08:35:26</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Namuna mijoz 3</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>+998 93 333 44 55</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Investor</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Investitsiya</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Bog‘lanildi</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Direksiya (namuna)</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>https://linverno-tm.github.io/oltinkol-zona/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
+      <c r="B57" t="n">
         <v>2</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-10-14 01:35:26</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Namuna mijoz 2</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+998 91 222 33 44</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Ulgurji xaridor</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ulgurji xarid</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Erkaklar poyabzali, 500 juft</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>Uchrashuv belgilandi</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
+      <c r="C57" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Biriktirilmagan</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>2</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
         <is>
           <t>Sotuv bo‘limi (namuna)</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>https://linverno-tm.github.io/oltinkol-zona/</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
+      <c r="B59" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" t="n">
         <v>1</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-10-13 18:35:26</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Namuna mijoz 1</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+998 90 111 22 33</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Ishlab chiqaruvchi</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Savdo do‘konini kreditga olish</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>A-05 do‘kon bo‘yicha</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Shartnoma</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>Sotuv bo‘limi (namuna)</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>https://linverno-tm.github.io/oltinkol-zona/</t>
-        </is>
+      <c r="D59" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="4">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/panel/arizalar.xlsx
+++ b/panel/arizalar.xlsx
@@ -914,7 +914,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>«Oltinko‘l tuman charm-poyabzal kichik sanoat zonasini boshqarish direksiyasi» MChJ · 15.10.2026 13:00 holatiga · jami 6 ta</t>
+          <t>«Oltinko‘l tuman charm-poyabzal kichik sanoat zonasini boshqarish direksiyasi» MChJ · 15.10.2026 14:37 holatiga · jami 6 ta</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>46310.25</v>
+        <v>46310.31736111111</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
+          <t>2026-10-15 14:37 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1029,7 +1029,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>46309.95833333334</v>
+        <v>46310.02569444444</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>46309.66666666666</v>
+        <v>46309.73402777778</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>46309.375</v>
+        <v>46309.44236111111</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
+          <t>2026-10-15 14:37 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>46309.08333333334</v>
+        <v>46309.15069444444</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
+          <t>2026-10-15 14:37 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1217,7 +1217,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>46308.79166666666</v>
+        <v>46308.85902777778</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15 13:00 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
+          <t>2026-10-15 14:37 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>«Oltinko‘l tuman charm-poyabzal kichik sanoat zonasini boshqarish direksiyasi» MChJ · 15.10.2026 13:00 holatiga</t>
+          <t>«Oltinko‘l tuman charm-poyabzal kichik sanoat zonasini boshqarish direksiyasi» MChJ · 15.10.2026 14:37 holatiga</t>
         </is>
       </c>
     </row>

--- a/panel/arizalar.xlsx
+++ b/panel/arizalar.xlsx
@@ -914,7 +914,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>«Oltinko‘l tuman charm-poyabzal kichik sanoat zonasini boshqarish direksiyasi» MChJ · 15.10.2026 14:37 holatiga · jami 6 ta</t>
+          <t>«Oltinko‘l tuman charm-poyabzal kichik sanoat zonasini boshqarish direksiyasi» MChJ · 15.10.2026 14:39 holatiga · jami 6 ta</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>46310.31736111111</v>
+        <v>46310.31875</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15 14:37 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
+          <t>2026-10-15 14:39 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1029,7 +1029,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>46310.02569444444</v>
+        <v>46310.02708333333</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>46309.73402777778</v>
+        <v>46309.73541666667</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>46309.44236111111</v>
+        <v>46309.44375</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15 14:37 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
+          <t>2026-10-15 14:39 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>46309.15069444444</v>
+        <v>46309.15208333333</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15 14:37 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
+          <t>2026-10-15 14:39 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1217,7 +1217,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>46308.85902777778</v>
+        <v>46308.86041666667</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15 14:37 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
+          <t>2026-10-15 14:39 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>«Oltinko‘l tuman charm-poyabzal kichik sanoat zonasini boshqarish direksiyasi» MChJ · 15.10.2026 14:37 holatiga</t>
+          <t>«Oltinko‘l tuman charm-poyabzal kichik sanoat zonasini boshqarish direksiyasi» MChJ · 15.10.2026 14:39 holatiga</t>
         </is>
       </c>
     </row>

--- a/panel/arizalar.xlsx
+++ b/panel/arizalar.xlsx
@@ -914,7 +914,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>«Oltinko‘l tuman charm-poyabzal kichik sanoat zonasini boshqarish direksiyasi» MChJ · 15.10.2026 14:39 holatiga · jami 6 ta</t>
+          <t>«Oltinko‘l tuman charm-poyabzal kichik sanoat zonasini boshqarish direksiyasi» MChJ · 15.10.2026 16:26 holatiga · jami 6 ta</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
         <v>6</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>46310.31875</v>
+        <v>46310.39305555556</v>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15 14:39 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
+          <t>2026-10-15 16:26 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -1029,7 +1029,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>46310.02708333333</v>
+        <v>46310.10138888889</v>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>46309.73541666667</v>
+        <v>46309.80972222222</v>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>46309.44375</v>
+        <v>46309.51805555556</v>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="J8" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15 14:39 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
+          <t>2026-10-15 16:26 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
@@ -1164,7 +1164,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>46309.15208333333</v>
+        <v>46309.22638888889</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15 14:39 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
+          <t>2026-10-15 16:26 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -1217,7 +1217,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>46308.86041666667</v>
+        <v>46308.93472222222</v>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="J10" s="7" t="inlineStr">
         <is>
-          <t>2026-10-15 14:39 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
+          <t>2026-10-15 16:26 · Direksiya (namuna): Qo‘ng‘iroq qildim, ma’lumot berdim</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>«Oltinko‘l tuman charm-poyabzal kichik sanoat zonasini boshqarish direksiyasi» MChJ · 15.10.2026 14:39 holatiga</t>
+          <t>«Oltinko‘l tuman charm-poyabzal kichik sanoat zonasini boshqarish direksiyasi» MChJ · 15.10.2026 16:26 holatiga</t>
         </is>
       </c>
     </row>
